--- a/quanta/dist/20261025_廣達模型_v0.2.xlsx
+++ b/quanta/dist/20261025_廣達模型_v0.2.xlsx
@@ -6026,7 +6026,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6263,7 +6263,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6384,7 +6384,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6505,7 +6505,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6626,7 +6626,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6747,7 +6747,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
